--- a/Taller_de_fundamentos_de_mecanica_2026-2/Notas/Notas_Taller_Mecanica_G14_2026-2.xlsx
+++ b/Taller_de_fundamentos_de_mecanica_2026-2/Notas/Notas_Taller_Mecanica_G14_2026-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\miguel_perdomo\Auxiliar_docente_UNAL\Taller_de_fundamentos_de_mecanica_2026-2\Notas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62631E60-9B87-46A8-8283-04AA8155D8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3CA1DA-35E9-4B43-BCA2-0AC2F1FD92F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="52680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="Resumen" sheetId="3" r:id="rId3"/>
     <sheet name="Configuración" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Notas!$A$3:$AC$39</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -601,7 +604,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,8 +710,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -761,6 +771,24 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF0FAF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -822,7 +850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -934,6 +962,14 @@
     <xf numFmtId="164" fontId="16" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1226,248 +1262,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
+      <c r="A3" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
+      <c r="B5" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
     </row>
     <row r="10" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
     </row>
     <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
     </row>
     <row r="18" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
     </row>
     <row r="19" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
     </row>
     <row r="20" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
     </row>
     <row r="21" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
     </row>
     <row r="23" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
     </row>
     <row r="24" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="42" t="s">
+      <c r="A26" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
     </row>
     <row r="27" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
     </row>
     <row r="29" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -1523,70 +1559,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-    </row>
-    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+    </row>
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
     </row>
     <row r="3" spans="1:29" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1690,7 +1726,9 @@
       <c r="D4" s="9">
         <v>7</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="10">
+        <v>5</v>
+      </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -1700,11 +1738,13 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
-      <c r="O4" s="11" t="str">
+      <c r="O4" s="11">
         <f t="shared" ref="O4:O34" si="0">IFERROR(AVERAGE(E4:N4),"")</f>
-        <v/>
-      </c>
-      <c r="P4" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P4" s="10">
+        <v>5</v>
+      </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
@@ -1714,20 +1754,20 @@
       <c r="W4" s="10"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
-      <c r="Z4" s="11" t="str">
+      <c r="Z4" s="11">
         <f t="shared" ref="Z4:Z34" si="1">IFERROR(AVERAGE(P4:Y4),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA4" s="12">
         <v>1</v>
       </c>
-      <c r="AB4" s="13" t="str">
+      <c r="AB4" s="13">
         <f>IFERROR((IF(O4="",0,O4*Configuración!$B$4)+IF(Z4="",0,Z4*Configuración!$B$5))/(IF(O4="",0,Configuración!$B$4)+IF(Z4="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC4" s="14" t="str">
         <f>IF(AB4="","",IF(AB4&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1743,7 +1783,9 @@
       <c r="D5" s="9">
         <v>6</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="10">
+        <v>5</v>
+      </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1753,11 +1795,13 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
-      <c r="O5" s="11" t="str">
+      <c r="O5" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P5" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P5" s="10">
+        <v>5</v>
+      </c>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
       <c r="S5" s="10"/>
@@ -1767,20 +1811,20 @@
       <c r="W5" s="10"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
-      <c r="Z5" s="11" t="str">
+      <c r="Z5" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA5" s="12">
         <v>1</v>
       </c>
-      <c r="AB5" s="13" t="str">
+      <c r="AB5" s="13">
         <f>IFERROR((IF(O5="",0,O5*Configuración!$B$4)+IF(Z5="",0,Z5*Configuración!$B$5))/(IF(O5="",0,Configuración!$B$4)+IF(Z5="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC5" s="14" t="str">
         <f>IF(AB5="","",IF(AB5&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1796,7 +1840,9 @@
       <c r="D6" s="9">
         <v>6</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="10">
+        <v>5</v>
+      </c>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -1806,11 +1852,13 @@
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
-      <c r="O6" s="11" t="str">
+      <c r="O6" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P6" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P6" s="10">
+        <v>5</v>
+      </c>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
@@ -1820,20 +1868,20 @@
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
-      <c r="Z6" s="11" t="str">
+      <c r="Z6" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA6" s="12">
         <v>1</v>
       </c>
-      <c r="AB6" s="13" t="str">
+      <c r="AB6" s="13">
         <f>IFERROR((IF(O6="",0,O6*Configuración!$B$4)+IF(Z6="",0,Z6*Configuración!$B$5))/(IF(O6="",0,Configuración!$B$4)+IF(Z6="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC6" s="14" t="str">
         <f>IF(AB6="","",IF(AB6&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1849,7 +1897,9 @@
       <c r="D7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="10"/>
+      <c r="E7" s="10">
+        <v>5</v>
+      </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -1859,11 +1909,13 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="11" t="str">
+      <c r="O7" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P7" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P7" s="10">
+        <v>5</v>
+      </c>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
@@ -1873,34 +1925,34 @@
       <c r="W7" s="10"/>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
-      <c r="Z7" s="11" t="str">
+      <c r="Z7" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA7" s="12">
         <v>1</v>
       </c>
-      <c r="AB7" s="13" t="str">
+      <c r="AB7" s="13">
         <f>IFERROR((IF(O7="",0,O7*Configuración!$B$4)+IF(Z7="",0,Z7*Configuración!$B$5))/(IF(O7="",0,Configuración!$B$4)+IF(Z7="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC7" s="14" t="str">
         <f>IF(AB7="","",IF(AB7&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="42" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="39" t="s">
         <v>154</v>
       </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="43"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -1914,7 +1966,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P8" s="10"/>
+      <c r="P8" s="43"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
@@ -1922,7 +1974,7 @@
       <c r="U8" s="10"/>
       <c r="V8" s="10"/>
       <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
+      <c r="X8" s="41"/>
       <c r="Y8" s="10"/>
       <c r="Z8" s="11" t="str">
         <f t="shared" si="1"/>
@@ -1953,7 +2005,9 @@
       <c r="D9" s="9">
         <v>8</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="10">
+        <v>5</v>
+      </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -1963,11 +2017,13 @@
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
-      <c r="O9" s="11" t="str">
+      <c r="O9" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P9" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P9" s="10">
+        <v>5</v>
+      </c>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
@@ -1977,34 +2033,34 @@
       <c r="W9" s="10"/>
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
-      <c r="Z9" s="11" t="str">
+      <c r="Z9" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA9" s="12">
         <v>1</v>
       </c>
-      <c r="AB9" s="13" t="str">
+      <c r="AB9" s="13">
         <f>IFERROR((IF(O9="",0,O9*Configuración!$B$4)+IF(Z9="",0,Z9*Configuración!$B$5))/(IF(O9="",0,Configuración!$B$4)+IF(Z9="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC9" s="14" t="str">
         <f>IF(AB9="","",IF(AB9&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="42" t="s">
         <v>121</v>
       </c>
       <c r="C10" s="39" t="s">
         <v>156</v>
       </c>
       <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="43"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -2018,7 +2074,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P10" s="10"/>
+      <c r="P10" s="43"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
@@ -2057,7 +2113,9 @@
       <c r="D11" s="9">
         <v>8</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="10">
+        <v>5</v>
+      </c>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -2067,11 +2125,13 @@
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
-      <c r="O11" s="11" t="str">
+      <c r="O11" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P11" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P11" s="10">
+        <v>5</v>
+      </c>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
@@ -2081,20 +2141,20 @@
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
-      <c r="Z11" s="11" t="str">
+      <c r="Z11" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA11" s="12">
         <v>1</v>
       </c>
-      <c r="AB11" s="13" t="str">
+      <c r="AB11" s="13">
         <f>IFERROR((IF(O11="",0,O11*Configuración!$B$4)+IF(Z11="",0,Z11*Configuración!$B$5))/(IF(O11="",0,Configuración!$B$4)+IF(Z11="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC11" s="14" t="str">
         <f>IF(AB11="","",IF(AB11&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2110,7 +2170,9 @@
       <c r="D12" s="9">
         <v>1</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="10">
+        <v>5</v>
+      </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -2120,11 +2182,13 @@
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
-      <c r="O12" s="11" t="str">
+      <c r="O12" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P12" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P12" s="10">
+        <v>5</v>
+      </c>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
@@ -2134,34 +2198,36 @@
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
-      <c r="Z12" s="11" t="str">
+      <c r="Z12" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA12" s="12">
         <v>1</v>
       </c>
-      <c r="AB12" s="13" t="str">
+      <c r="AB12" s="13">
         <f>IFERROR((IF(O12="",0,O12*Configuración!$B$4)+IF(Z12="",0,Z12*Configuración!$B$5))/(IF(O12="",0,Configuración!$B$4)+IF(Z12="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC12" s="14" t="str">
         <f>IF(AB12="","",IF(AB12&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="44" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="39" t="s">
         <v>159</v>
       </c>
       <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
@@ -2171,11 +2237,11 @@
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
-      <c r="O13" s="11" t="str">
+      <c r="O13" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P13" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="P13" s="43"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
@@ -2192,13 +2258,13 @@
       <c r="AA13" s="12">
         <v>1</v>
       </c>
-      <c r="AB13" s="13" t="str">
+      <c r="AB13" s="13">
         <f>IFERROR((IF(O13="",0,O13*Configuración!$B$4)+IF(Z13="",0,Z13*Configuración!$B$5))/(IF(O13="",0,Configuración!$B$4)+IF(Z13="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC13" s="14" t="str">
         <f>IF(AB13="","",IF(AB13&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>REPROBADO</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2214,7 +2280,9 @@
       <c r="D14" s="9">
         <v>5</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="10">
+        <v>5</v>
+      </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -2224,11 +2292,13 @@
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
-      <c r="O14" s="11" t="str">
+      <c r="O14" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P14" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P14" s="10">
+        <v>5</v>
+      </c>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
@@ -2238,20 +2308,20 @@
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
-      <c r="Z14" s="11" t="str">
+      <c r="Z14" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA14" s="12">
         <v>1</v>
       </c>
-      <c r="AB14" s="13" t="str">
+      <c r="AB14" s="13">
         <f>IFERROR((IF(O14="",0,O14*Configuración!$B$4)+IF(Z14="",0,Z14*Configuración!$B$5))/(IF(O14="",0,Configuración!$B$4)+IF(Z14="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC14" s="14" t="str">
         <f>IF(AB14="","",IF(AB14&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2267,7 +2337,9 @@
       <c r="D15" s="9">
         <v>4</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="10">
+        <v>5</v>
+      </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -2277,11 +2349,13 @@
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
-      <c r="O15" s="11" t="str">
+      <c r="O15" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P15" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P15" s="10">
+        <v>5</v>
+      </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
@@ -2291,20 +2365,20 @@
       <c r="W15" s="10"/>
       <c r="X15" s="10"/>
       <c r="Y15" s="10"/>
-      <c r="Z15" s="11" t="str">
+      <c r="Z15" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA15" s="12">
         <v>1</v>
       </c>
-      <c r="AB15" s="13" t="str">
+      <c r="AB15" s="13">
         <f>IFERROR((IF(O15="",0,O15*Configuración!$B$4)+IF(Z15="",0,Z15*Configuración!$B$5))/(IF(O15="",0,Configuración!$B$4)+IF(Z15="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC15" s="14" t="str">
         <f>IF(AB15="","",IF(AB15&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2320,7 +2394,9 @@
       <c r="D16" s="9">
         <v>4</v>
       </c>
-      <c r="E16" s="10"/>
+      <c r="E16" s="10">
+        <v>5</v>
+      </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
@@ -2330,11 +2406,13 @@
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
-      <c r="O16" s="11" t="str">
+      <c r="O16" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P16" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P16" s="10">
+        <v>5</v>
+      </c>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
@@ -2344,34 +2422,34 @@
       <c r="W16" s="10"/>
       <c r="X16" s="10"/>
       <c r="Y16" s="10"/>
-      <c r="Z16" s="11" t="str">
+      <c r="Z16" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA16" s="12">
         <v>1</v>
       </c>
-      <c r="AB16" s="13" t="str">
+      <c r="AB16" s="13">
         <f>IFERROR((IF(O16="",0,O16*Configuración!$B$4)+IF(Z16="",0,Z16*Configuración!$B$5))/(IF(O16="",0,Configuración!$B$4)+IF(Z16="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC16" s="14" t="str">
         <f>IF(AB16="","",IF(AB16&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>14</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="42" t="s">
         <v>128</v>
       </c>
       <c r="C17" s="39" t="s">
         <v>163</v>
       </c>
       <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
+      <c r="E17" s="43"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -2385,7 +2463,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P17" s="10"/>
+      <c r="P17" s="43"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
@@ -2424,7 +2502,9 @@
       <c r="D18" s="9">
         <v>5</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="10">
+        <v>5</v>
+      </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -2434,11 +2514,13 @@
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
-      <c r="O18" s="11" t="str">
+      <c r="O18" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P18" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P18" s="10">
+        <v>5</v>
+      </c>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
@@ -2448,20 +2530,20 @@
       <c r="W18" s="10"/>
       <c r="X18" s="10"/>
       <c r="Y18" s="10"/>
-      <c r="Z18" s="11" t="str">
+      <c r="Z18" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA18" s="12">
         <v>1</v>
       </c>
-      <c r="AB18" s="13" t="str">
+      <c r="AB18" s="13">
         <f>IFERROR((IF(O18="",0,O18*Configuración!$B$4)+IF(Z18="",0,Z18*Configuración!$B$5))/(IF(O18="",0,Configuración!$B$4)+IF(Z18="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC18" s="14" t="str">
         <f>IF(AB18="","",IF(AB18&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2477,7 +2559,9 @@
       <c r="D19" s="9">
         <v>3</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="10">
+        <v>5</v>
+      </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -2487,11 +2571,13 @@
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
-      <c r="O19" s="11" t="str">
+      <c r="O19" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P19" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P19" s="10">
+        <v>5</v>
+      </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
@@ -2501,34 +2587,36 @@
       <c r="W19" s="10"/>
       <c r="X19" s="10"/>
       <c r="Y19" s="10"/>
-      <c r="Z19" s="11" t="str">
+      <c r="Z19" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA19" s="12">
         <v>1</v>
       </c>
-      <c r="AB19" s="13" t="str">
+      <c r="AB19" s="13">
         <f>IFERROR((IF(O19="",0,O19*Configuración!$B$4)+IF(Z19="",0,Z19*Configuración!$B$5))/(IF(O19="",0,Configuración!$B$4)+IF(Z19="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC19" s="14" t="str">
         <f>IF(AB19="","",IF(AB19&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>17</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="44" t="s">
         <v>131</v>
       </c>
       <c r="C20" s="39" t="s">
         <v>166</v>
       </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
+      <c r="E20" s="10">
+        <v>2.5</v>
+      </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -2538,11 +2626,11 @@
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
-      <c r="O20" s="11" t="str">
+      <c r="O20" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P20" s="10"/>
+        <v>2.5</v>
+      </c>
+      <c r="P20" s="43"/>
       <c r="Q20" s="10"/>
       <c r="R20" s="10"/>
       <c r="S20" s="10"/>
@@ -2559,13 +2647,13 @@
       <c r="AA20" s="12">
         <v>1</v>
       </c>
-      <c r="AB20" s="13" t="str">
+      <c r="AB20" s="13">
         <f>IFERROR((IF(O20="",0,O20*Configuración!$B$4)+IF(Z20="",0,Z20*Configuración!$B$5))/(IF(O20="",0,Configuración!$B$4)+IF(Z20="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="AC20" s="14" t="str">
         <f>IF(AB20="","",IF(AB20&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>REPROBADO</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2581,7 +2669,9 @@
       <c r="D21" s="9">
         <v>3</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="10">
+        <v>5</v>
+      </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -2591,11 +2681,13 @@
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="11" t="str">
+      <c r="O21" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P21" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P21" s="10">
+        <v>5</v>
+      </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
@@ -2605,20 +2697,20 @@
       <c r="W21" s="10"/>
       <c r="X21" s="10"/>
       <c r="Y21" s="10"/>
-      <c r="Z21" s="11" t="str">
+      <c r="Z21" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA21" s="12">
         <v>1</v>
       </c>
-      <c r="AB21" s="13" t="str">
+      <c r="AB21" s="13">
         <f>IFERROR((IF(O21="",0,O21*Configuración!$B$4)+IF(Z21="",0,Z21*Configuración!$B$5))/(IF(O21="",0,Configuración!$B$4)+IF(Z21="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC21" s="14" t="str">
         <f>IF(AB21="","",IF(AB21&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2634,7 +2726,9 @@
       <c r="D22" s="9">
         <v>4</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="10">
+        <v>5</v>
+      </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -2644,11 +2738,13 @@
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
       <c r="N22" s="10"/>
-      <c r="O22" s="11" t="str">
+      <c r="O22" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P22" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P22" s="10">
+        <v>5</v>
+      </c>
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="10"/>
@@ -2658,20 +2754,20 @@
       <c r="W22" s="10"/>
       <c r="X22" s="10"/>
       <c r="Y22" s="10"/>
-      <c r="Z22" s="11" t="str">
+      <c r="Z22" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA22" s="12">
         <v>1</v>
       </c>
-      <c r="AB22" s="13" t="str">
+      <c r="AB22" s="13">
         <f>IFERROR((IF(O22="",0,O22*Configuración!$B$4)+IF(Z22="",0,Z22*Configuración!$B$5))/(IF(O22="",0,Configuración!$B$4)+IF(Z22="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC22" s="14" t="str">
         <f>IF(AB22="","",IF(AB22&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2687,7 +2783,9 @@
       <c r="D23" s="9">
         <v>5</v>
       </c>
-      <c r="E23" s="10"/>
+      <c r="E23" s="10">
+        <v>5</v>
+      </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -2697,11 +2795,13 @@
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
       <c r="N23" s="10"/>
-      <c r="O23" s="11" t="str">
+      <c r="O23" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P23" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P23" s="10">
+        <v>5</v>
+      </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="10"/>
@@ -2711,27 +2811,27 @@
       <c r="W23" s="10"/>
       <c r="X23" s="10"/>
       <c r="Y23" s="10"/>
-      <c r="Z23" s="11" t="str">
+      <c r="Z23" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA23" s="12">
         <v>1</v>
       </c>
-      <c r="AB23" s="13" t="str">
+      <c r="AB23" s="13">
         <f>IFERROR((IF(O23="",0,O23*Configuración!$B$4)+IF(Z23="",0,Z23*Configuración!$B$5))/(IF(O23="",0,Configuración!$B$4)+IF(Z23="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC23" s="14" t="str">
         <f>IF(AB23="","",IF(AB23&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>21</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="42" t="s">
         <v>135</v>
       </c>
       <c r="C24" s="39" t="s">
@@ -2740,7 +2840,7 @@
       <c r="D24" s="9">
         <v>8</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="43"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -2754,7 +2854,9 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="P24" s="10"/>
+      <c r="P24" s="10">
+        <v>5</v>
+      </c>
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10"/>
@@ -2764,20 +2866,20 @@
       <c r="W24" s="10"/>
       <c r="X24" s="10"/>
       <c r="Y24" s="10"/>
-      <c r="Z24" s="11" t="str">
+      <c r="Z24" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA24" s="12">
         <v>1</v>
       </c>
-      <c r="AB24" s="13" t="str">
+      <c r="AB24" s="13">
         <f>IFERROR((IF(O24="",0,O24*Configuración!$B$4)+IF(Z24="",0,Z24*Configuración!$B$5))/(IF(O24="",0,Configuración!$B$4)+IF(Z24="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC24" s="14" t="str">
         <f>IF(AB24="","",IF(AB24&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2793,7 +2895,9 @@
       <c r="D25" s="9">
         <v>7</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="10">
+        <v>5</v>
+      </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -2803,11 +2907,13 @@
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
-      <c r="O25" s="11" t="str">
+      <c r="O25" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P25" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P25" s="10">
+        <v>5</v>
+      </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
@@ -2817,20 +2923,20 @@
       <c r="W25" s="10"/>
       <c r="X25" s="10"/>
       <c r="Y25" s="10"/>
-      <c r="Z25" s="11" t="str">
+      <c r="Z25" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA25" s="12">
         <v>1</v>
       </c>
-      <c r="AB25" s="13" t="str">
+      <c r="AB25" s="13">
         <f>IFERROR((IF(O25="",0,O25*Configuración!$B$4)+IF(Z25="",0,Z25*Configuración!$B$5))/(IF(O25="",0,Configuración!$B$4)+IF(Z25="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC25" s="14" t="str">
         <f>IF(AB25="","",IF(AB25&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2846,7 +2952,9 @@
       <c r="D26" s="9">
         <v>2</v>
       </c>
-      <c r="E26" s="10"/>
+      <c r="E26" s="10">
+        <v>5</v>
+      </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -2856,11 +2964,13 @@
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
       <c r="N26" s="10"/>
-      <c r="O26" s="11" t="str">
+      <c r="O26" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P26" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P26" s="10">
+        <v>5</v>
+      </c>
       <c r="Q26" s="10"/>
       <c r="R26" s="10"/>
       <c r="S26" s="10"/>
@@ -2870,20 +2980,20 @@
       <c r="W26" s="10"/>
       <c r="X26" s="10"/>
       <c r="Y26" s="10"/>
-      <c r="Z26" s="11" t="str">
+      <c r="Z26" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA26" s="12">
         <v>1</v>
       </c>
-      <c r="AB26" s="13" t="str">
+      <c r="AB26" s="13">
         <f>IFERROR((IF(O26="",0,O26*Configuración!$B$4)+IF(Z26="",0,Z26*Configuración!$B$5))/(IF(O26="",0,Configuración!$B$4)+IF(Z26="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC26" s="14" t="str">
         <f>IF(AB26="","",IF(AB26&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2899,7 +3009,9 @@
       <c r="D27" s="9">
         <v>1</v>
       </c>
-      <c r="E27" s="10"/>
+      <c r="E27" s="10">
+        <v>5</v>
+      </c>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -2909,11 +3021,13 @@
       <c r="L27" s="10"/>
       <c r="M27" s="10"/>
       <c r="N27" s="10"/>
-      <c r="O27" s="11" t="str">
+      <c r="O27" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P27" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P27" s="10">
+        <v>5</v>
+      </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="10"/>
@@ -2923,20 +3037,20 @@
       <c r="W27" s="10"/>
       <c r="X27" s="10"/>
       <c r="Y27" s="10"/>
-      <c r="Z27" s="11" t="str">
+      <c r="Z27" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA27" s="12">
         <v>1</v>
       </c>
-      <c r="AB27" s="13" t="str">
+      <c r="AB27" s="13">
         <f>IFERROR((IF(O27="",0,O27*Configuración!$B$4)+IF(Z27="",0,Z27*Configuración!$B$5))/(IF(O27="",0,Configuración!$B$4)+IF(Z27="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC27" s="14" t="str">
         <f>IF(AB27="","",IF(AB27&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2952,7 +3066,9 @@
       <c r="D28" s="9">
         <v>7</v>
       </c>
-      <c r="E28" s="10"/>
+      <c r="E28" s="10">
+        <v>5</v>
+      </c>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
@@ -2962,11 +3078,13 @@
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
-      <c r="O28" s="11" t="str">
+      <c r="O28" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P28" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P28" s="10">
+        <v>5</v>
+      </c>
       <c r="Q28" s="10"/>
       <c r="R28" s="10"/>
       <c r="S28" s="10"/>
@@ -2976,20 +3094,20 @@
       <c r="W28" s="10"/>
       <c r="X28" s="10"/>
       <c r="Y28" s="10"/>
-      <c r="Z28" s="11" t="str">
+      <c r="Z28" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA28" s="12">
         <v>1</v>
       </c>
-      <c r="AB28" s="13" t="str">
+      <c r="AB28" s="13">
         <f>IFERROR((IF(O28="",0,O28*Configuración!$B$4)+IF(Z28="",0,Z28*Configuración!$B$5))/(IF(O28="",0,Configuración!$B$4)+IF(Z28="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC28" s="14" t="str">
         <f>IF(AB28="","",IF(AB28&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3005,7 +3123,9 @@
       <c r="D29" s="9">
         <v>3</v>
       </c>
-      <c r="E29" s="10"/>
+      <c r="E29" s="10">
+        <v>5</v>
+      </c>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
@@ -3015,11 +3135,13 @@
       <c r="L29" s="10"/>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
-      <c r="O29" s="11" t="str">
+      <c r="O29" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P29" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P29" s="10">
+        <v>5</v>
+      </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
@@ -3029,20 +3151,20 @@
       <c r="W29" s="10"/>
       <c r="X29" s="10"/>
       <c r="Y29" s="10"/>
-      <c r="Z29" s="11" t="str">
+      <c r="Z29" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA29" s="12">
         <v>1</v>
       </c>
-      <c r="AB29" s="13" t="str">
+      <c r="AB29" s="13">
         <f>IFERROR((IF(O29="",0,O29*Configuración!$B$4)+IF(Z29="",0,Z29*Configuración!$B$5))/(IF(O29="",0,Configuración!$B$4)+IF(Z29="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC29" s="14" t="str">
         <f>IF(AB29="","",IF(AB29&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3058,7 +3180,9 @@
       <c r="D30" s="9">
         <v>2</v>
       </c>
-      <c r="E30" s="10"/>
+      <c r="E30" s="10">
+        <v>5</v>
+      </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -3068,11 +3192,13 @@
       <c r="L30" s="10"/>
       <c r="M30" s="10"/>
       <c r="N30" s="10"/>
-      <c r="O30" s="11" t="str">
+      <c r="O30" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P30" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P30" s="10">
+        <v>5</v>
+      </c>
       <c r="Q30" s="10"/>
       <c r="R30" s="10"/>
       <c r="S30" s="10"/>
@@ -3082,34 +3208,36 @@
       <c r="W30" s="10"/>
       <c r="X30" s="10"/>
       <c r="Y30" s="10"/>
-      <c r="Z30" s="11" t="str">
+      <c r="Z30" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA30" s="12">
         <v>1</v>
       </c>
-      <c r="AB30" s="13" t="str">
+      <c r="AB30" s="13">
         <f>IFERROR((IF(O30="",0,O30*Configuración!$B$4)+IF(Z30="",0,Z30*Configuración!$B$5))/(IF(O30="",0,Configuración!$B$4)+IF(Z30="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC30" s="14" t="str">
         <f>IF(AB30="","",IF(AB30&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>28</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="44" t="s">
         <v>142</v>
       </c>
       <c r="C31" s="39" t="s">
         <v>177</v>
       </c>
       <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
+      <c r="E31" s="10">
+        <v>5</v>
+      </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -3119,11 +3247,11 @@
       <c r="L31" s="10"/>
       <c r="M31" s="10"/>
       <c r="N31" s="10"/>
-      <c r="O31" s="11" t="str">
+      <c r="O31" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P31" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P31" s="43"/>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="10"/>
@@ -3140,13 +3268,13 @@
       <c r="AA31" s="12">
         <v>1</v>
       </c>
-      <c r="AB31" s="13" t="str">
+      <c r="AB31" s="13">
         <f>IFERROR((IF(O31="",0,O31*Configuración!$B$4)+IF(Z31="",0,Z31*Configuración!$B$5))/(IF(O31="",0,Configuración!$B$4)+IF(Z31="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC31" s="14" t="str">
         <f>IF(AB31="","",IF(AB31&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="32" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3162,7 +3290,9 @@
       <c r="D32" s="9">
         <v>8</v>
       </c>
-      <c r="E32" s="10"/>
+      <c r="E32" s="10">
+        <v>5</v>
+      </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
@@ -3172,11 +3302,13 @@
       <c r="L32" s="10"/>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
-      <c r="O32" s="11" t="str">
+      <c r="O32" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P32" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P32" s="10">
+        <v>5</v>
+      </c>
       <c r="Q32" s="10"/>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
@@ -3186,20 +3318,20 @@
       <c r="W32" s="10"/>
       <c r="X32" s="10"/>
       <c r="Y32" s="10"/>
-      <c r="Z32" s="11" t="str">
+      <c r="Z32" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA32" s="12">
         <v>1</v>
       </c>
-      <c r="AB32" s="13" t="str">
+      <c r="AB32" s="13">
         <f>IFERROR((IF(O32="",0,O32*Configuración!$B$4)+IF(Z32="",0,Z32*Configuración!$B$5))/(IF(O32="",0,Configuración!$B$4)+IF(Z32="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC32" s="14" t="str">
         <f>IF(AB32="","",IF(AB32&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3215,7 +3347,9 @@
       <c r="D33" s="9">
         <v>2</v>
       </c>
-      <c r="E33" s="10"/>
+      <c r="E33" s="10">
+        <v>5</v>
+      </c>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
@@ -3225,11 +3359,13 @@
       <c r="L33" s="10"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10"/>
-      <c r="O33" s="11" t="str">
+      <c r="O33" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P33" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P33" s="10">
+        <v>5</v>
+      </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
@@ -3239,20 +3375,20 @@
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
       <c r="Y33" s="10"/>
-      <c r="Z33" s="11" t="str">
+      <c r="Z33" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA33" s="12">
         <v>1</v>
       </c>
-      <c r="AB33" s="13" t="str">
+      <c r="AB33" s="13">
         <f>IFERROR((IF(O33="",0,O33*Configuración!$B$4)+IF(Z33="",0,Z33*Configuración!$B$5))/(IF(O33="",0,Configuración!$B$4)+IF(Z33="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC33" s="14" t="str">
         <f>IF(AB33="","",IF(AB33&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3268,7 +3404,9 @@
       <c r="D34" s="9">
         <v>4</v>
       </c>
-      <c r="E34" s="10"/>
+      <c r="E34" s="10">
+        <v>5</v>
+      </c>
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
@@ -3278,11 +3416,13 @@
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
-      <c r="O34" s="11" t="str">
+      <c r="O34" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P34" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P34" s="10">
+        <v>5</v>
+      </c>
       <c r="Q34" s="10"/>
       <c r="R34" s="10"/>
       <c r="S34" s="10"/>
@@ -3292,20 +3432,20 @@
       <c r="W34" s="10"/>
       <c r="X34" s="10"/>
       <c r="Y34" s="10"/>
-      <c r="Z34" s="11" t="str">
+      <c r="Z34" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA34" s="12">
         <v>1</v>
       </c>
-      <c r="AB34" s="13" t="str">
+      <c r="AB34" s="13">
         <f>IFERROR((IF(O34="",0,O34*Configuración!$B$4)+IF(Z34="",0,Z34*Configuración!$B$5))/(IF(O34="",0,Configuración!$B$4)+IF(Z34="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC34" s="14" t="str">
         <f>IF(AB34="","",IF(AB34&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3321,7 +3461,9 @@
       <c r="D35" s="9">
         <v>7</v>
       </c>
-      <c r="E35" s="10"/>
+      <c r="E35" s="10">
+        <v>5</v>
+      </c>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
@@ -3331,11 +3473,13 @@
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
-      <c r="O35" s="11" t="str">
+      <c r="O35" s="11">
         <f t="shared" ref="O35:O38" si="2">IFERROR(AVERAGE(E35:N35),"")</f>
-        <v/>
-      </c>
-      <c r="P35" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P35" s="10">
+        <v>5</v>
+      </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
       <c r="S35" s="10"/>
@@ -3345,20 +3489,20 @@
       <c r="W35" s="10"/>
       <c r="X35" s="10"/>
       <c r="Y35" s="10"/>
-      <c r="Z35" s="11" t="str">
+      <c r="Z35" s="11">
         <f t="shared" ref="Z35:Z38" si="3">IFERROR(AVERAGE(P35:Y35),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA35" s="12">
         <v>1</v>
       </c>
-      <c r="AB35" s="13" t="str">
+      <c r="AB35" s="13">
         <f>IFERROR((IF(O35="",0,O35*Configuración!$B$4)+IF(Z35="",0,Z35*Configuración!$B$5))/(IF(O35="",0,Configuración!$B$4)+IF(Z35="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC35" s="14" t="str">
         <f>IF(AB35="","",IF(AB35&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
@@ -3374,7 +3518,9 @@
       <c r="D36" s="9">
         <v>2</v>
       </c>
-      <c r="E36" s="10"/>
+      <c r="E36" s="10">
+        <v>5</v>
+      </c>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
@@ -3384,11 +3530,13 @@
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
-      <c r="O36" s="11" t="str">
+      <c r="O36" s="11">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P36" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P36" s="10">
+        <v>5</v>
+      </c>
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="10"/>
@@ -3398,20 +3546,20 @@
       <c r="W36" s="10"/>
       <c r="X36" s="10"/>
       <c r="Y36" s="10"/>
-      <c r="Z36" s="11" t="str">
+      <c r="Z36" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA36" s="12">
         <v>1</v>
       </c>
-      <c r="AB36" s="13" t="str">
+      <c r="AB36" s="13">
         <f>IFERROR((IF(O36="",0,O36*Configuración!$B$4)+IF(Z36="",0,Z36*Configuración!$B$5))/(IF(O36="",0,Configuración!$B$4)+IF(Z36="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC36" s="14" t="str">
         <f>IF(AB36="","",IF(AB36&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
@@ -3427,7 +3575,9 @@
       <c r="D37" s="9">
         <v>5</v>
       </c>
-      <c r="E37" s="10"/>
+      <c r="E37" s="10">
+        <v>5</v>
+      </c>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -3437,11 +3587,13 @@
       <c r="L37" s="10"/>
       <c r="M37" s="10"/>
       <c r="N37" s="10"/>
-      <c r="O37" s="11" t="str">
+      <c r="O37" s="11">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P37" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P37" s="10">
+        <v>5</v>
+      </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
@@ -3451,20 +3603,20 @@
       <c r="W37" s="10"/>
       <c r="X37" s="10"/>
       <c r="Y37" s="10"/>
-      <c r="Z37" s="11" t="str">
+      <c r="Z37" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA37" s="12">
         <v>1</v>
       </c>
-      <c r="AB37" s="13" t="str">
+      <c r="AB37" s="13">
         <f>IFERROR((IF(O37="",0,O37*Configuración!$B$4)+IF(Z37="",0,Z37*Configuración!$B$5))/(IF(O37="",0,Configuración!$B$4)+IF(Z37="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC37" s="14" t="str">
         <f>IF(AB37="","",IF(AB37&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
@@ -3480,7 +3632,9 @@
       <c r="D38" s="9">
         <v>1</v>
       </c>
-      <c r="E38" s="10"/>
+      <c r="E38" s="10">
+        <v>5</v>
+      </c>
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
@@ -3490,11 +3644,13 @@
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
-      <c r="O38" s="11" t="str">
+      <c r="O38" s="11">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P38" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="P38" s="10">
+        <v>5</v>
+      </c>
       <c r="Q38" s="10"/>
       <c r="R38" s="10"/>
       <c r="S38" s="10"/>
@@ -3504,20 +3660,20 @@
       <c r="W38" s="10"/>
       <c r="X38" s="10"/>
       <c r="Y38" s="10"/>
-      <c r="Z38" s="11" t="str">
+      <c r="Z38" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA38" s="12">
         <v>1</v>
       </c>
-      <c r="AB38" s="13" t="str">
+      <c r="AB38" s="13">
         <f>IFERROR((IF(O38="",0,O38*Configuración!$B$4)+IF(Z38="",0,Z38*Configuración!$B$5))/(IF(O38="",0,Configuración!$B$4)+IF(Z38="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC38" s="14" t="str">
         <f>IF(AB38="","",IF(AB38&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
@@ -3527,9 +3683,9 @@
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
-      <c r="E39" s="17" t="str">
+      <c r="E39" s="17">
         <f t="shared" ref="E39" si="4">IFERROR(AVERAGE(E8:E38),"")</f>
-        <v/>
+        <v>4.7592592592592595</v>
       </c>
       <c r="F39" s="17" t="str">
         <f t="shared" ref="F39" si="5">IFERROR(AVERAGE(F8:F38),"")</f>
@@ -3567,13 +3723,13 @@
         <f t="shared" ref="N39" si="13">IFERROR(AVERAGE(N8:N38),"")</f>
         <v/>
       </c>
-      <c r="O39" s="18" t="str">
+      <c r="O39" s="18">
         <f t="shared" ref="O39" si="14">IFERROR(AVERAGE(O8:O38),"")</f>
-        <v/>
-      </c>
-      <c r="P39" s="17" t="str">
+        <v>4.7592592592592595</v>
+      </c>
+      <c r="P39" s="17">
         <f t="shared" ref="P39" si="15">IFERROR(AVERAGE(P8:P38),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q39" s="17" t="str">
         <f t="shared" ref="Q39" si="16">IFERROR(AVERAGE(Q8:Q38),"")</f>
@@ -3611,24 +3767,25 @@
         <f t="shared" ref="Y39" si="24">IFERROR(AVERAGE(Y8:Y38),"")</f>
         <v/>
       </c>
-      <c r="Z39" s="18" t="str">
+      <c r="Z39" s="18">
         <f t="shared" ref="Z39" si="25">IFERROR(AVERAGE(Z8:Z38),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA39" s="19">
         <f t="shared" ref="AA39" si="26">IFERROR(AVERAGE(AA8:AA38),"")</f>
         <v>1</v>
       </c>
-      <c r="AB39" s="20" t="str">
+      <c r="AB39" s="20">
         <f t="shared" ref="AB39" si="27">IFERROR(AVERAGE(AB8:AB38),"")</f>
-        <v/>
+        <v>4.7678571428571432</v>
       </c>
       <c r="AC39" s="21" t="str">
         <f t="shared" ref="AC39" si="28">COUNTIF(AC8:AC38,"APROBADO")&amp;" aprob."</f>
-        <v>0 aprob.</v>
+        <v>26 aprob.</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:AC39" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="A2:AC2"/>
@@ -3651,25 +3808,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="D3" s="42" t="s">
+      <c r="B3" s="46"/>
+      <c r="D3" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
@@ -3695,7 +3852,7 @@
       </c>
       <c r="B5" s="23">
         <f>COUNT(Notas!$AB$4:$AB$34)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D5" s="25">
         <v>1</v>
@@ -3704,18 +3861,18 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D5)</f>
         <v>2</v>
       </c>
-      <c r="F5" s="27" t="str">
+      <c r="F5" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D5,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="28" t="str">
+      <c r="B6" s="28">
         <f>IFERROR(AVERAGE(Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>4.7678571428571432</v>
       </c>
       <c r="D6" s="25">
         <v>2</v>
@@ -3724,9 +3881,9 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D6)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="27" t="str">
+      <c r="F6" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D6,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3735,7 +3892,7 @@
       </c>
       <c r="B7" s="28">
         <f>IFERROR(MAX(Notas!$AB$4:$AB$34),"")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="25">
         <v>3</v>
@@ -3744,9 +3901,9 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D7)</f>
         <v>4</v>
       </c>
-      <c r="F7" s="27" t="str">
+      <c r="F7" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D7,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3755,7 +3912,7 @@
       </c>
       <c r="B8" s="28">
         <f>IFERROR(MIN(Notas!$AB$4:$AB$34),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="25">
         <v>4</v>
@@ -3764,18 +3921,18 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D8)</f>
         <v>4</v>
       </c>
-      <c r="F8" s="27" t="str">
+      <c r="F8" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D8,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="28" t="str">
+      <c r="B9" s="28">
         <f>IFERROR(STDEV(Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>0.87646325119073376</v>
       </c>
       <c r="D9" s="25">
         <v>5</v>
@@ -3784,9 +3941,9 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D9)</f>
         <v>3</v>
       </c>
-      <c r="F9" s="27" t="str">
+      <c r="F9" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D9,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3795,7 +3952,7 @@
       </c>
       <c r="B10" s="23">
         <f>COUNTIF(Notas!$AC$4:$AC$34,"APROBADO")</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D10" s="25">
         <v>6</v>
@@ -3804,9 +3961,9 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D10)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="27" t="str">
+      <c r="F10" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D10,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3815,7 +3972,7 @@
       </c>
       <c r="B11" s="23">
         <f>COUNTIF(Notas!$AC$4:$AC$34,"REPROBADO")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="25">
         <v>7</v>
@@ -3824,9 +3981,9 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D11)</f>
         <v>3</v>
       </c>
-      <c r="F11" s="27" t="str">
+      <c r="F11" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D11,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3844,18 +4001,18 @@
         <f>COUNTIF(Notas!$D$4:$D$34,$D12)</f>
         <v>4</v>
       </c>
-      <c r="F12" s="27" t="str">
+      <c r="F12" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D12,Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="29" t="str">
+      <c r="B13" s="29">
         <f>IFERROR(COUNTIF(Notas!$AC$4:$AC$34,"APROBADO")/COUNT(Notas!$AB$4:$AB$34),"")</f>
-        <v/>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D13" s="25">
         <v>9</v>
@@ -3883,23 +4040,23 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="D16" s="42" t="s">
+      <c r="B16" s="46"/>
+      <c r="D16" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B17" s="28">
         <f>IFERROR(AVERAGE(Notas!$Z$4:$Z$34),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>89</v>
@@ -3912,16 +4069,16 @@
       <c r="A18" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="28" t="str">
+      <c r="B18" s="28">
         <f>IFERROR(AVERAGE(Notas!$O$4:$O$34),"")</f>
-        <v/>
+        <v>4.7592592592592595</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>92</v>
       </c>
       <c r="E18" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;0,Notas!$AB$4:$AB$34,"&lt;"&amp;2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -3932,7 +4089,7 @@
       </c>
       <c r="E19" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;2,Notas!$AB$4:$AB$34,"&lt;"&amp;3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -3970,7 +4127,7 @@
       </c>
       <c r="E23" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;4.5,Notas!$AB$4:$AB$34,"&lt;"&amp;5.01)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3997,11 +4154,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4052,11 +4209,11 @@
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
@@ -4082,11 +4239,11 @@
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">

--- a/Taller_de_fundamentos_de_mecanica_2026-2/Notas/Notas_Taller_Mecanica_G14_2026-2.xlsx
+++ b/Taller_de_fundamentos_de_mecanica_2026-2/Notas/Notas_Taller_Mecanica_G14_2026-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\miguel_perdomo\Auxiliar_docente_UNAL\Taller_de_fundamentos_de_mecanica_2026-2\Notas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3CA1DA-35E9-4B43-BCA2-0AC2F1FD92F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08D1F9B-8392-4572-BBA9-72DF61715B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="188">
   <si>
     <t>CÓMO USAR ESTE LIBRO — Taller de Fundamentos de Mecánica (1000019), Grupo 14</t>
   </si>
@@ -595,6 +595,15 @@
   </si>
   <si>
     <t>jozapatam@unal.edu.co</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1729,7 +1738,9 @@
       <c r="E4" s="10">
         <v>5</v>
       </c>
-      <c r="F4" s="10"/>
+      <c r="F4" s="10">
+        <v>5</v>
+      </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
@@ -1745,8 +1756,12 @@
       <c r="P4" s="10">
         <v>5</v>
       </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
+      <c r="Q4" s="10">
+        <v>5</v>
+      </c>
+      <c r="R4" s="10">
+        <v>5</v>
+      </c>
       <c r="S4" s="10"/>
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
@@ -1786,7 +1801,9 @@
       <c r="E5" s="10">
         <v>5</v>
       </c>
-      <c r="F5" s="10"/>
+      <c r="F5" s="10">
+        <v>5</v>
+      </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
@@ -1802,8 +1819,12 @@
       <c r="P5" s="10">
         <v>5</v>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
+      <c r="Q5" s="10">
+        <v>5</v>
+      </c>
+      <c r="R5" s="10">
+        <v>5</v>
+      </c>
       <c r="S5" s="10"/>
       <c r="T5" s="10"/>
       <c r="U5" s="10"/>
@@ -1843,7 +1864,9 @@
       <c r="E6" s="10">
         <v>5</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="10">
+        <v>5</v>
+      </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
@@ -1859,8 +1882,12 @@
       <c r="P6" s="10">
         <v>5</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
+      <c r="Q6" s="10">
+        <v>5</v>
+      </c>
+      <c r="R6" s="10">
+        <v>5</v>
+      </c>
       <c r="S6" s="10"/>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
@@ -1900,7 +1927,9 @@
       <c r="E7" s="10">
         <v>5</v>
       </c>
-      <c r="F7" s="10"/>
+      <c r="F7" s="10">
+        <v>5</v>
+      </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
@@ -1916,8 +1945,12 @@
       <c r="P7" s="10">
         <v>5</v>
       </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
+      <c r="Q7" s="10">
+        <v>5</v>
+      </c>
+      <c r="R7" s="10">
+        <v>5</v>
+      </c>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
@@ -1953,7 +1986,9 @@
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="43"/>
-      <c r="F8" s="10"/>
+      <c r="F8" s="43">
+        <v>1</v>
+      </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
@@ -1962,9 +1997,9 @@
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
-      <c r="O8" s="11" t="str">
+      <c r="O8" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P8" s="43"/>
       <c r="Q8" s="10"/>
@@ -1983,13 +2018,13 @@
       <c r="AA8" s="12">
         <v>1</v>
       </c>
-      <c r="AB8" s="13" t="str">
+      <c r="AB8" s="13">
         <f>IFERROR((IF(O8="",0,O8*Configuración!$B$4)+IF(Z8="",0,Z8*Configuración!$B$5))/(IF(O8="",0,Configuración!$B$4)+IF(Z8="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC8" s="14" t="str">
         <f>IF(AB8="","",IF(AB8&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>REPROBADO</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2008,7 +2043,9 @@
       <c r="E9" s="10">
         <v>5</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="10" t="s">
+        <v>186</v>
+      </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
@@ -2024,8 +2061,12 @@
       <c r="P9" s="10">
         <v>5</v>
       </c>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
+      <c r="Q9" s="10">
+        <v>5</v>
+      </c>
+      <c r="R9" s="10">
+        <v>5</v>
+      </c>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
       <c r="U9" s="10"/>
@@ -2059,9 +2100,13 @@
       <c r="C10" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="9">
+        <v>5</v>
+      </c>
       <c r="E10" s="43"/>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <v>2</v>
+      </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
@@ -2070,13 +2115,19 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
-      <c r="O10" s="11" t="str">
+      <c r="O10" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
+        <v>2</v>
+      </c>
+      <c r="P10" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>5</v>
+      </c>
+      <c r="R10" s="10">
+        <v>5</v>
+      </c>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
       <c r="U10" s="10"/>
@@ -2084,20 +2135,20 @@
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
-      <c r="Z10" s="11" t="str">
+      <c r="Z10" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA10" s="12">
         <v>1</v>
       </c>
-      <c r="AB10" s="13" t="str">
+      <c r="AB10" s="13">
         <f>IFERROR((IF(O10="",0,O10*Configuración!$B$4)+IF(Z10="",0,Z10*Configuración!$B$5))/(IF(O10="",0,Configuración!$B$4)+IF(Z10="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="AC10" s="14" t="str">
         <f>IF(AB10="","",IF(AB10&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2116,7 +2167,9 @@
       <c r="E11" s="10">
         <v>5</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="10">
+        <v>5</v>
+      </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -2132,8 +2185,12 @@
       <c r="P11" s="10">
         <v>5</v>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
+      <c r="Q11" s="10">
+        <v>5</v>
+      </c>
+      <c r="R11" s="10">
+        <v>5</v>
+      </c>
       <c r="S11" s="10"/>
       <c r="T11" s="10"/>
       <c r="U11" s="10"/>
@@ -2173,7 +2230,9 @@
       <c r="E12" s="10">
         <v>5</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="10">
+        <v>5</v>
+      </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -2189,8 +2248,12 @@
       <c r="P12" s="10">
         <v>5</v>
       </c>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
+      <c r="Q12" s="10">
+        <v>5</v>
+      </c>
+      <c r="R12" s="10">
+        <v>5</v>
+      </c>
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
       <c r="U12" s="10"/>
@@ -2224,11 +2287,15 @@
       <c r="C13" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9">
+        <v>2</v>
+      </c>
       <c r="E13" s="10">
         <v>1</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="10">
+        <v>5</v>
+      </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
@@ -2239,11 +2306,17 @@
       <c r="N13" s="10"/>
       <c r="O13" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
+        <v>3</v>
+      </c>
+      <c r="P13" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>5</v>
+      </c>
+      <c r="R13" s="10">
+        <v>5</v>
+      </c>
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
       <c r="U13" s="10"/>
@@ -2251,20 +2324,20 @@
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
-      <c r="Z13" s="11" t="str">
+      <c r="Z13" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA13" s="12">
         <v>1</v>
       </c>
       <c r="AB13" s="13">
         <f>IFERROR((IF(O13="",0,O13*Configuración!$B$4)+IF(Z13="",0,Z13*Configuración!$B$5))/(IF(O13="",0,Configuración!$B$4)+IF(Z13="",0,Configuración!$B$5)),"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC13" s="14" t="str">
         <f>IF(AB13="","",IF(AB13&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v>REPROBADO</v>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2283,7 +2356,9 @@
       <c r="E14" s="10">
         <v>5</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="10">
+        <v>3</v>
+      </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
@@ -2294,13 +2369,17 @@
       <c r="N14" s="10"/>
       <c r="O14" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P14" s="10">
         <v>5</v>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
+      <c r="Q14" s="10">
+        <v>5</v>
+      </c>
+      <c r="R14" s="10">
+        <v>5</v>
+      </c>
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
       <c r="U14" s="10"/>
@@ -2317,7 +2396,7 @@
       </c>
       <c r="AB14" s="13">
         <f>IFERROR((IF(O14="",0,O14*Configuración!$B$4)+IF(Z14="",0,Z14*Configuración!$B$5))/(IF(O14="",0,Configuración!$B$4)+IF(Z14="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AC14" s="14" t="str">
         <f>IF(AB14="","",IF(AB14&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -2340,7 +2419,9 @@
       <c r="E15" s="10">
         <v>5</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="10">
+        <v>5</v>
+      </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
@@ -2356,8 +2437,12 @@
       <c r="P15" s="10">
         <v>5</v>
       </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
+      <c r="Q15" s="10">
+        <v>5</v>
+      </c>
+      <c r="R15" s="10">
+        <v>5</v>
+      </c>
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
       <c r="U15" s="10"/>
@@ -2397,7 +2482,9 @@
       <c r="E16" s="10">
         <v>5</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
@@ -2408,13 +2495,17 @@
       <c r="N16" s="10"/>
       <c r="O16" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P16" s="10">
         <v>5</v>
       </c>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
+      <c r="Q16" s="10">
+        <v>5</v>
+      </c>
+      <c r="R16" s="10">
+        <v>5</v>
+      </c>
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
       <c r="U16" s="10"/>
@@ -2431,7 +2522,7 @@
       </c>
       <c r="AB16" s="13">
         <f>IFERROR((IF(O16="",0,O16*Configuración!$B$4)+IF(Z16="",0,Z16*Configuración!$B$5))/(IF(O16="",0,Configuración!$B$4)+IF(Z16="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC16" s="14" t="str">
         <f>IF(AB16="","",IF(AB16&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -2450,7 +2541,9 @@
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="43"/>
-      <c r="F17" s="10"/>
+      <c r="F17" s="43">
+        <v>1</v>
+      </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
@@ -2459,9 +2552,9 @@
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
-      <c r="O17" s="11" t="str">
+      <c r="O17" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P17" s="43"/>
       <c r="Q17" s="10"/>
@@ -2480,13 +2573,13 @@
       <c r="AA17" s="12">
         <v>1</v>
       </c>
-      <c r="AB17" s="13" t="str">
+      <c r="AB17" s="13">
         <f>IFERROR((IF(O17="",0,O17*Configuración!$B$4)+IF(Z17="",0,Z17*Configuración!$B$5))/(IF(O17="",0,Configuración!$B$4)+IF(Z17="",0,Configuración!$B$5)),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC17" s="14" t="str">
         <f>IF(AB17="","",IF(AB17&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v/>
+        <v>REPROBADO</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2505,7 +2598,9 @@
       <c r="E18" s="10">
         <v>5</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="10">
+        <v>5</v>
+      </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
@@ -2521,8 +2616,12 @@
       <c r="P18" s="10">
         <v>5</v>
       </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
+      <c r="Q18" s="10">
+        <v>5</v>
+      </c>
+      <c r="R18" s="10">
+        <v>5</v>
+      </c>
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
       <c r="U18" s="10"/>
@@ -2562,7 +2661,9 @@
       <c r="E19" s="10">
         <v>5</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10">
+        <v>5</v>
+      </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
@@ -2578,8 +2679,12 @@
       <c r="P19" s="10">
         <v>5</v>
       </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
+      <c r="Q19" s="10">
+        <v>5</v>
+      </c>
+      <c r="R19" s="10">
+        <v>5</v>
+      </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
@@ -2613,11 +2718,15 @@
       <c r="C20" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="9">
+        <v>3</v>
+      </c>
       <c r="E20" s="10">
         <v>2.5</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="43">
+        <v>1</v>
+      </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
@@ -2628,11 +2737,15 @@
       <c r="N20" s="10"/>
       <c r="O20" s="11">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="P20" s="43"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
+      <c r="Q20" s="10">
+        <v>5</v>
+      </c>
+      <c r="R20" s="10">
+        <v>5</v>
+      </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
       <c r="U20" s="10"/>
@@ -2640,20 +2753,20 @@
       <c r="W20" s="10"/>
       <c r="X20" s="10"/>
       <c r="Y20" s="10"/>
-      <c r="Z20" s="11" t="str">
+      <c r="Z20" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA20" s="12">
         <v>1</v>
       </c>
       <c r="AB20" s="13">
         <f>IFERROR((IF(O20="",0,O20*Configuración!$B$4)+IF(Z20="",0,Z20*Configuración!$B$5))/(IF(O20="",0,Configuración!$B$4)+IF(Z20="",0,Configuración!$B$5)),"")</f>
-        <v>2.5</v>
+        <v>3.375</v>
       </c>
       <c r="AC20" s="14" t="str">
         <f>IF(AB20="","",IF(AB20&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
-        <v>REPROBADO</v>
+        <v>APROBADO</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2672,7 +2785,9 @@
       <c r="E21" s="10">
         <v>5</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="10">
+        <v>5</v>
+      </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
@@ -2688,8 +2803,12 @@
       <c r="P21" s="10">
         <v>5</v>
       </c>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
+      <c r="Q21" s="10">
+        <v>5</v>
+      </c>
+      <c r="R21" s="10">
+        <v>5</v>
+      </c>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
       <c r="U21" s="10"/>
@@ -2729,7 +2848,9 @@
       <c r="E22" s="10">
         <v>5</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="43">
+        <v>1</v>
+      </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
@@ -2740,13 +2861,17 @@
       <c r="N22" s="10"/>
       <c r="O22" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P22" s="10">
         <v>5</v>
       </c>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
+      <c r="Q22" s="10">
+        <v>5</v>
+      </c>
+      <c r="R22" s="10">
+        <v>5</v>
+      </c>
       <c r="S22" s="10"/>
       <c r="T22" s="10"/>
       <c r="U22" s="10"/>
@@ -2763,7 +2888,7 @@
       </c>
       <c r="AB22" s="13">
         <f>IFERROR((IF(O22="",0,O22*Configuración!$B$4)+IF(Z22="",0,Z22*Configuración!$B$5))/(IF(O22="",0,Configuración!$B$4)+IF(Z22="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC22" s="14" t="str">
         <f>IF(AB22="","",IF(AB22&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -2786,7 +2911,9 @@
       <c r="E23" s="10">
         <v>5</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="10">
+        <v>2</v>
+      </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
@@ -2797,17 +2924,23 @@
       <c r="N23" s="10"/>
       <c r="O23" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P23" s="10">
         <v>5</v>
       </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
+      <c r="Q23" s="10">
+        <v>5</v>
+      </c>
+      <c r="R23" s="10">
+        <v>5</v>
+      </c>
       <c r="S23" s="10"/>
       <c r="T23" s="10"/>
       <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
+      <c r="V23" s="10" t="s">
+        <v>187</v>
+      </c>
       <c r="W23" s="10"/>
       <c r="X23" s="10"/>
       <c r="Y23" s="10"/>
@@ -2820,7 +2953,7 @@
       </c>
       <c r="AB23" s="13">
         <f>IFERROR((IF(O23="",0,O23*Configuración!$B$4)+IF(Z23="",0,Z23*Configuración!$B$5))/(IF(O23="",0,Configuración!$B$4)+IF(Z23="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AC23" s="14" t="str">
         <f>IF(AB23="","",IF(AB23&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -2841,7 +2974,9 @@
         <v>8</v>
       </c>
       <c r="E24" s="43"/>
-      <c r="F24" s="10"/>
+      <c r="F24" s="43">
+        <v>1</v>
+      </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
@@ -2850,15 +2985,19 @@
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
       <c r="N24" s="10"/>
-      <c r="O24" s="11" t="str">
+      <c r="O24" s="11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P24" s="10">
         <v>5</v>
       </c>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
+      <c r="Q24" s="10">
+        <v>5</v>
+      </c>
+      <c r="R24" s="10">
+        <v>5</v>
+      </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
       <c r="U24" s="10"/>
@@ -2875,7 +3014,7 @@
       </c>
       <c r="AB24" s="13">
         <f>IFERROR((IF(O24="",0,O24*Configuración!$B$4)+IF(Z24="",0,Z24*Configuración!$B$5))/(IF(O24="",0,Configuración!$B$4)+IF(Z24="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC24" s="14" t="str">
         <f>IF(AB24="","",IF(AB24&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -2898,7 +3037,9 @@
       <c r="E25" s="10">
         <v>5</v>
       </c>
-      <c r="F25" s="10"/>
+      <c r="F25" s="43">
+        <v>1</v>
+      </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
@@ -2909,13 +3050,17 @@
       <c r="N25" s="10"/>
       <c r="O25" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P25" s="10">
         <v>5</v>
       </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
+      <c r="Q25" s="10">
+        <v>5</v>
+      </c>
+      <c r="R25" s="10">
+        <v>5</v>
+      </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
       <c r="U25" s="10"/>
@@ -2932,7 +3077,7 @@
       </c>
       <c r="AB25" s="13">
         <f>IFERROR((IF(O25="",0,O25*Configuración!$B$4)+IF(Z25="",0,Z25*Configuración!$B$5))/(IF(O25="",0,Configuración!$B$4)+IF(Z25="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC25" s="14" t="str">
         <f>IF(AB25="","",IF(AB25&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -2955,7 +3100,9 @@
       <c r="E26" s="10">
         <v>5</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="10">
+        <v>2</v>
+      </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
@@ -2966,13 +3113,17 @@
       <c r="N26" s="10"/>
       <c r="O26" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P26" s="10">
         <v>5</v>
       </c>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
+      <c r="Q26" s="10">
+        <v>5</v>
+      </c>
+      <c r="R26" s="10">
+        <v>5</v>
+      </c>
       <c r="S26" s="10"/>
       <c r="T26" s="10"/>
       <c r="U26" s="10"/>
@@ -2989,7 +3140,7 @@
       </c>
       <c r="AB26" s="13">
         <f>IFERROR((IF(O26="",0,O26*Configuración!$B$4)+IF(Z26="",0,Z26*Configuración!$B$5))/(IF(O26="",0,Configuración!$B$4)+IF(Z26="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AC26" s="14" t="str">
         <f>IF(AB26="","",IF(AB26&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3012,7 +3163,9 @@
       <c r="E27" s="10">
         <v>5</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="10">
+        <v>4</v>
+      </c>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
@@ -3023,13 +3176,17 @@
       <c r="N27" s="10"/>
       <c r="O27" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P27" s="10">
         <v>5</v>
       </c>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
+      <c r="Q27" s="10">
+        <v>5</v>
+      </c>
+      <c r="R27" s="10">
+        <v>5</v>
+      </c>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="10"/>
@@ -3046,7 +3203,7 @@
       </c>
       <c r="AB27" s="13">
         <f>IFERROR((IF(O27="",0,O27*Configuración!$B$4)+IF(Z27="",0,Z27*Configuración!$B$5))/(IF(O27="",0,Configuración!$B$4)+IF(Z27="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC27" s="14" t="str">
         <f>IF(AB27="","",IF(AB27&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3069,7 +3226,9 @@
       <c r="E28" s="10">
         <v>5</v>
       </c>
-      <c r="F28" s="10"/>
+      <c r="F28" s="10">
+        <v>2</v>
+      </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
@@ -3080,13 +3239,17 @@
       <c r="N28" s="10"/>
       <c r="O28" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P28" s="10">
         <v>5</v>
       </c>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
+      <c r="Q28" s="10">
+        <v>5</v>
+      </c>
+      <c r="R28" s="10">
+        <v>5</v>
+      </c>
       <c r="S28" s="10"/>
       <c r="T28" s="10"/>
       <c r="U28" s="10"/>
@@ -3103,7 +3266,7 @@
       </c>
       <c r="AB28" s="13">
         <f>IFERROR((IF(O28="",0,O28*Configuración!$B$4)+IF(Z28="",0,Z28*Configuración!$B$5))/(IF(O28="",0,Configuración!$B$4)+IF(Z28="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AC28" s="14" t="str">
         <f>IF(AB28="","",IF(AB28&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3126,7 +3289,9 @@
       <c r="E29" s="10">
         <v>5</v>
       </c>
-      <c r="F29" s="10"/>
+      <c r="F29" s="10" t="s">
+        <v>185</v>
+      </c>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
@@ -3142,8 +3307,12 @@
       <c r="P29" s="10">
         <v>5</v>
       </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
+      <c r="Q29" s="10">
+        <v>5</v>
+      </c>
+      <c r="R29" s="10">
+        <v>5</v>
+      </c>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
       <c r="U29" s="10"/>
@@ -3183,7 +3352,9 @@
       <c r="E30" s="10">
         <v>5</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="10" t="s">
+        <v>186</v>
+      </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
@@ -3199,8 +3370,12 @@
       <c r="P30" s="10">
         <v>5</v>
       </c>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
+      <c r="Q30" s="10">
+        <v>5</v>
+      </c>
+      <c r="R30" s="10">
+        <v>5</v>
+      </c>
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
       <c r="U30" s="10"/>
@@ -3234,11 +3409,15 @@
       <c r="C31" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="D31" s="9"/>
+      <c r="D31" s="9">
+        <v>1</v>
+      </c>
       <c r="E31" s="10">
         <v>5</v>
       </c>
-      <c r="F31" s="10"/>
+      <c r="F31" s="10">
+        <v>2</v>
+      </c>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
@@ -3249,11 +3428,17 @@
       <c r="N31" s="10"/>
       <c r="O31" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
+        <v>3.5</v>
+      </c>
+      <c r="P31" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>5</v>
+      </c>
+      <c r="R31" s="10">
+        <v>5</v>
+      </c>
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
       <c r="U31" s="10"/>
@@ -3261,16 +3446,16 @@
       <c r="W31" s="10"/>
       <c r="X31" s="10"/>
       <c r="Y31" s="10"/>
-      <c r="Z31" s="11" t="str">
+      <c r="Z31" s="11">
         <f t="shared" si="1"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA31" s="12">
         <v>1</v>
       </c>
       <c r="AB31" s="13">
         <f>IFERROR((IF(O31="",0,O31*Configuración!$B$4)+IF(Z31="",0,Z31*Configuración!$B$5))/(IF(O31="",0,Configuración!$B$4)+IF(Z31="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AC31" s="14" t="str">
         <f>IF(AB31="","",IF(AB31&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3293,7 +3478,9 @@
       <c r="E32" s="10">
         <v>5</v>
       </c>
-      <c r="F32" s="10"/>
+      <c r="F32" s="43">
+        <v>1</v>
+      </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
@@ -3304,13 +3491,17 @@
       <c r="N32" s="10"/>
       <c r="O32" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P32" s="10">
         <v>5</v>
       </c>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
+      <c r="Q32" s="10">
+        <v>5</v>
+      </c>
+      <c r="R32" s="10">
+        <v>5</v>
+      </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
@@ -3327,7 +3518,7 @@
       </c>
       <c r="AB32" s="13">
         <f>IFERROR((IF(O32="",0,O32*Configuración!$B$4)+IF(Z32="",0,Z32*Configuración!$B$5))/(IF(O32="",0,Configuración!$B$4)+IF(Z32="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC32" s="14" t="str">
         <f>IF(AB32="","",IF(AB32&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3350,7 +3541,9 @@
       <c r="E33" s="10">
         <v>5</v>
       </c>
-      <c r="F33" s="10"/>
+      <c r="F33" s="10">
+        <v>5</v>
+      </c>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
@@ -3366,8 +3559,12 @@
       <c r="P33" s="10">
         <v>5</v>
       </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
+      <c r="Q33" s="10">
+        <v>5</v>
+      </c>
+      <c r="R33" s="10">
+        <v>5</v>
+      </c>
       <c r="S33" s="10"/>
       <c r="T33" s="10"/>
       <c r="U33" s="10"/>
@@ -3407,7 +3604,9 @@
       <c r="E34" s="10">
         <v>5</v>
       </c>
-      <c r="F34" s="10"/>
+      <c r="F34" s="43">
+        <v>1</v>
+      </c>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
@@ -3418,13 +3617,17 @@
       <c r="N34" s="10"/>
       <c r="O34" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P34" s="10">
         <v>5</v>
       </c>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
+      <c r="Q34" s="10">
+        <v>5</v>
+      </c>
+      <c r="R34" s="10">
+        <v>5</v>
+      </c>
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
       <c r="U34" s="10"/>
@@ -3441,7 +3644,7 @@
       </c>
       <c r="AB34" s="13">
         <f>IFERROR((IF(O34="",0,O34*Configuración!$B$4)+IF(Z34="",0,Z34*Configuración!$B$5))/(IF(O34="",0,Configuración!$B$4)+IF(Z34="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC34" s="14" t="str">
         <f>IF(AB34="","",IF(AB34&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3464,7 +3667,9 @@
       <c r="E35" s="10">
         <v>5</v>
       </c>
-      <c r="F35" s="10"/>
+      <c r="F35" s="10">
+        <v>5</v>
+      </c>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -3480,8 +3685,12 @@
       <c r="P35" s="10">
         <v>5</v>
       </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
+      <c r="Q35" s="10">
+        <v>5</v>
+      </c>
+      <c r="R35" s="10">
+        <v>5</v>
+      </c>
       <c r="S35" s="10"/>
       <c r="T35" s="10"/>
       <c r="U35" s="10"/>
@@ -3521,7 +3730,9 @@
       <c r="E36" s="10">
         <v>5</v>
       </c>
-      <c r="F36" s="10"/>
+      <c r="F36" s="10">
+        <v>5</v>
+      </c>
       <c r="G36" s="10"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -3537,8 +3748,12 @@
       <c r="P36" s="10">
         <v>5</v>
       </c>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
+      <c r="Q36" s="10">
+        <v>5</v>
+      </c>
+      <c r="R36" s="10">
+        <v>5</v>
+      </c>
       <c r="S36" s="10"/>
       <c r="T36" s="10"/>
       <c r="U36" s="10"/>
@@ -3578,7 +3793,9 @@
       <c r="E37" s="10">
         <v>5</v>
       </c>
-      <c r="F37" s="10"/>
+      <c r="F37" s="10">
+        <v>5</v>
+      </c>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -3594,8 +3811,12 @@
       <c r="P37" s="10">
         <v>5</v>
       </c>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
+      <c r="Q37" s="10">
+        <v>5</v>
+      </c>
+      <c r="R37" s="10">
+        <v>5</v>
+      </c>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
       <c r="U37" s="10"/>
@@ -3635,7 +3856,9 @@
       <c r="E38" s="10">
         <v>5</v>
       </c>
-      <c r="F38" s="10"/>
+      <c r="F38" s="10">
+        <v>2</v>
+      </c>
       <c r="G38" s="10"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
@@ -3646,13 +3869,17 @@
       <c r="N38" s="10"/>
       <c r="O38" s="11">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P38" s="10">
         <v>5</v>
       </c>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
+      <c r="Q38" s="10">
+        <v>5</v>
+      </c>
+      <c r="R38" s="10">
+        <v>5</v>
+      </c>
       <c r="S38" s="10"/>
       <c r="T38" s="10"/>
       <c r="U38" s="10"/>
@@ -3669,7 +3896,7 @@
       </c>
       <c r="AB38" s="13">
         <f>IFERROR((IF(O38="",0,O38*Configuración!$B$4)+IF(Z38="",0,Z38*Configuración!$B$5))/(IF(O38="",0,Configuración!$B$4)+IF(Z38="",0,Configuración!$B$5)),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AC38" s="14" t="str">
         <f>IF(AB38="","",IF(AB38&gt;=Configuración!$B$9,"APROBADO","REPROBADO"))</f>
@@ -3687,9 +3914,9 @@
         <f t="shared" ref="E39" si="4">IFERROR(AVERAGE(E8:E38),"")</f>
         <v>4.7592592592592595</v>
       </c>
-      <c r="F39" s="17" t="str">
+      <c r="F39" s="17">
         <f t="shared" ref="F39" si="5">IFERROR(AVERAGE(F8:F38),"")</f>
-        <v/>
+        <v>2.9642857142857144</v>
       </c>
       <c r="G39" s="17" t="str">
         <f t="shared" ref="G39" si="6">IFERROR(AVERAGE(G8:G38),"")</f>
@@ -3725,19 +3952,19 @@
       </c>
       <c r="O39" s="18">
         <f t="shared" ref="O39" si="14">IFERROR(AVERAGE(O8:O38),"")</f>
-        <v>4.7592592592592595</v>
+        <v>3.7338709677419355</v>
       </c>
       <c r="P39" s="17">
         <f t="shared" ref="P39" si="15">IFERROR(AVERAGE(P8:P38),"")</f>
         <v>5</v>
       </c>
-      <c r="Q39" s="17" t="str">
+      <c r="Q39" s="17">
         <f t="shared" ref="Q39" si="16">IFERROR(AVERAGE(Q8:Q38),"")</f>
-        <v/>
-      </c>
-      <c r="R39" s="17" t="str">
+        <v>5</v>
+      </c>
+      <c r="R39" s="17">
         <f t="shared" ref="R39" si="17">IFERROR(AVERAGE(R8:R38),"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S39" s="17" t="str">
         <f t="shared" ref="S39" si="18">IFERROR(AVERAGE(S8:S38),"")</f>
@@ -3777,11 +4004,11 @@
       </c>
       <c r="AB39" s="20">
         <f t="shared" ref="AB39" si="27">IFERROR(AVERAGE(AB8:AB38),"")</f>
-        <v>4.7678571428571432</v>
+        <v>4.237903225806452</v>
       </c>
       <c r="AC39" s="21" t="str">
         <f t="shared" ref="AC39" si="28">COUNTIF(AC8:AC38,"APROBADO")&amp;" aprob."</f>
-        <v>26 aprob.</v>
+        <v>29 aprob.</v>
       </c>
     </row>
   </sheetData>
@@ -3852,18 +4079,18 @@
       </c>
       <c r="B5" s="23">
         <f>COUNT(Notas!$AB$4:$AB$34)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" s="25">
         <v>1</v>
       </c>
       <c r="E5" s="26">
         <f>COUNTIF(Notas!$D$4:$D$34,$D5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D5,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3872,18 +4099,18 @@
       </c>
       <c r="B6" s="28">
         <f>IFERROR(AVERAGE(Notas!$AB$4:$AB$34),"")</f>
-        <v>4.7678571428571432</v>
+        <v>4.262096774193548</v>
       </c>
       <c r="D6" s="25">
         <v>2</v>
       </c>
       <c r="E6" s="26">
         <f>COUNTIF(Notas!$D$4:$D$34,$D6)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D6,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.5625</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3899,11 +4126,11 @@
       </c>
       <c r="E7" s="26">
         <f>COUNTIF(Notas!$D$4:$D$34,$D7)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D7,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.6749999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3923,7 +4150,7 @@
       </c>
       <c r="F8" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D8,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,18 +4159,18 @@
       </c>
       <c r="B9" s="28">
         <f>IFERROR(STDEV(Notas!$AB$4:$AB$34),"")</f>
-        <v>0.87646325119073376</v>
+        <v>1.0420106958772455</v>
       </c>
       <c r="D9" s="25">
         <v>5</v>
       </c>
       <c r="E9" s="26">
         <f>COUNTIF(Notas!$D$4:$D$34,$D9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D9,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.3125</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3952,7 +4179,7 @@
       </c>
       <c r="B10" s="23">
         <f>COUNTIF(Notas!$AC$4:$AC$34,"APROBADO")</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" s="25">
         <v>6</v>
@@ -3983,7 +4210,7 @@
       </c>
       <c r="F11" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D11,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.416666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4003,7 +4230,7 @@
       </c>
       <c r="F12" s="27">
         <f>IFERROR(AVERAGEIF(Notas!$D$4:$D$34,$D12,Notas!$AB$4:$AB$34),"")</f>
-        <v>5</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4012,7 +4239,7 @@
       </c>
       <c r="B13" s="29">
         <f>IFERROR(COUNTIF(Notas!$AC$4:$AC$34,"APROBADO")/COUNT(Notas!$AB$4:$AB$34),"")</f>
-        <v>0.9285714285714286</v>
+        <v>0.93548387096774188</v>
       </c>
       <c r="D13" s="25">
         <v>9</v>
@@ -4071,14 +4298,14 @@
       </c>
       <c r="B18" s="28">
         <f>IFERROR(AVERAGE(Notas!$O$4:$O$34),"")</f>
-        <v>4.7592592592592595</v>
+        <v>3.782258064516129</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>92</v>
       </c>
       <c r="E18" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;0,Notas!$AB$4:$AB$34,"&lt;"&amp;2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -4089,7 +4316,7 @@
       </c>
       <c r="E19" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;2,Notas!$AB$4:$AB$34,"&lt;"&amp;3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -4100,7 +4327,7 @@
       </c>
       <c r="E20" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;3,Notas!$AB$4:$AB$34,"&lt;"&amp;3.5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -4109,7 +4336,7 @@
       </c>
       <c r="E21" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;3.5,Notas!$AB$4:$AB$34,"&lt;"&amp;4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -4118,7 +4345,7 @@
       </c>
       <c r="E22" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;4,Notas!$AB$4:$AB$34,"&lt;"&amp;4.5)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -4127,7 +4354,7 @@
       </c>
       <c r="E23" s="23">
         <f>COUNTIFS(Notas!$AB$4:$AB$34,"&gt;="&amp;4.5,Notas!$AB$4:$AB$34,"&lt;"&amp;5.01)</f>
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
